--- a/docs/要件設計.xlsx
+++ b/docs/要件設計.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tk-sasaki\Documents\開発演習\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tk-sasaki\Documents\event-application-system\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB0E7611-C20A-499F-98F2-F62DB3B82DDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C5F1A95-C159-4CD8-B1D6-58459A5F2A02}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10170" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="要件設計" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1099" uniqueCount="652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1117" uniqueCount="670">
   <si>
     <t>テーマ：イベント申込システム</t>
   </si>
@@ -2441,12 +2441,65 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>NOT NULL, FK→events.id</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>NOT NULL, DEFAULT '受付済'</t>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>VARCHAR(1000)</t>
+  </si>
+  <si>
+    <t>NOT NULL, FK→events.id, ON DELETE CASCADE（要確認・推奨値）</t>
+  </si>
+  <si>
+    <t>インデックス一覧</t>
+  </si>
+  <si>
+    <t>テーブル</t>
+  </si>
+  <si>
+    <t>インデックス名</t>
+  </si>
+  <si>
+    <t>対象列</t>
+  </si>
+  <si>
+    <t>用途</t>
+  </si>
+  <si>
+    <t>events</t>
+  </si>
+  <si>
+    <t>idx_events_start_at</t>
+  </si>
+  <si>
+    <t>start_at</t>
+  </si>
+  <si>
+    <t>一覧の開催日時昇順ソート（API-01）</t>
+  </si>
+  <si>
+    <t>applications</t>
+  </si>
+  <si>
+    <t>idx_app_event_status_user</t>
+  </si>
+  <si>
+    <t>event_id, status, user_id</t>
+  </si>
+  <si>
+    <t>定員超過チェック・充足率集計（event_id+status）、二重申込チェック（+user_id）</t>
+  </si>
+  <si>
+    <t>idx_app_user_applied</t>
+  </si>
+  <si>
+    <t>user_id, applied_at</t>
+  </si>
+  <si>
+    <t>マイページの自分の申込一覧（API-04、申込日時順）</t>
+  </si>
+  <si>
+    <t>※ user_id／event_id 単体には、FK制約によりMySQL(InnoDB)が自動でインデックスを作成する。</t>
   </si>
 </sst>
 </file>
@@ -2499,7 +2552,7 @@
       <charset val="128"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2524,6 +2577,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2624,23 +2683,23 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -4338,66 +4397,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="22.5" x14ac:dyDescent="0.65">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>540</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="15" t="s">
         <v>49</v>
       </c>
-      <c r="B3" s="12"/>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="B4" s="12"/>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+      <c r="G5" s="13"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="B7" s="12"/>
-      <c r="C7" s="12"/>
-      <c r="D7" s="12"/>
-      <c r="E7" s="12"/>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12"/>
+      <c r="B7" s="13"/>
+      <c r="C7" s="13"/>
+      <c r="D7" s="13"/>
+      <c r="E7" s="13"/>
+      <c r="F7" s="13"/>
+      <c r="G7" s="13"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A8" s="14" t="s">
+      <c r="A8" s="11" t="s">
         <v>53</v>
       </c>
       <c r="B8" s="10"/>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="11" t="s">
         <v>54</v>
       </c>
       <c r="D8" s="9"/>
@@ -4510,154 +4569,154 @@
       <c r="G16" s="10"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A18" s="13" t="s">
+      <c r="A18" s="15" t="s">
         <v>71</v>
       </c>
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A19" s="15" t="s">
+      <c r="A19" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="B20" s="12"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A21" s="11" t="s">
+      <c r="A21" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="B21" s="12"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="12"/>
-      <c r="E21" s="12"/>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A22" s="11" t="s">
+      <c r="A22" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="B22" s="12"/>
-      <c r="C22" s="12"/>
-      <c r="D22" s="12"/>
-      <c r="E22" s="12"/>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="13"/>
+      <c r="F22" s="13"/>
+      <c r="G22" s="13"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A23" s="11" t="s">
+      <c r="A23" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="B23" s="12"/>
-      <c r="C23" s="12"/>
-      <c r="D23" s="12"/>
-      <c r="E23" s="12"/>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="13"/>
+      <c r="F23" s="13"/>
+      <c r="G23" s="13"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A24" s="15" t="s">
+      <c r="A24" s="14" t="s">
         <v>77</v>
       </c>
-      <c r="B24" s="12"/>
-      <c r="C24" s="12"/>
-      <c r="D24" s="12"/>
-      <c r="E24" s="12"/>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A25" s="11" t="s">
+      <c r="A25" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="B25" s="12"/>
-      <c r="C25" s="12"/>
-      <c r="D25" s="12"/>
-      <c r="E25" s="12"/>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="13"/>
+      <c r="F25" s="13"/>
+      <c r="G25" s="13"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A26" s="11" t="s">
+      <c r="A26" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="B26" s="12"/>
-      <c r="C26" s="12"/>
-      <c r="D26" s="12"/>
-      <c r="E26" s="12"/>
-      <c r="F26" s="12"/>
-      <c r="G26" s="12"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="13"/>
+      <c r="F26" s="13"/>
+      <c r="G26" s="13"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A27" s="11" t="s">
+      <c r="A27" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="B27" s="12"/>
-      <c r="C27" s="12"/>
-      <c r="D27" s="12"/>
-      <c r="E27" s="12"/>
-      <c r="F27" s="12"/>
-      <c r="G27" s="12"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="13"/>
+      <c r="F27" s="13"/>
+      <c r="G27" s="13"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A28" s="11" t="s">
+      <c r="A28" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="B28" s="12"/>
-      <c r="C28" s="12"/>
-      <c r="D28" s="12"/>
-      <c r="E28" s="12"/>
-      <c r="F28" s="12"/>
-      <c r="G28" s="12"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="13"/>
+      <c r="F28" s="13"/>
+      <c r="G28" s="13"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A29" s="11" t="s">
+      <c r="A29" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="12"/>
-      <c r="G29" s="12"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A31" s="13" t="s">
+      <c r="A31" s="15" t="s">
         <v>83</v>
       </c>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A32" s="14" t="s">
+      <c r="A32" s="11" t="s">
         <v>84</v>
       </c>
       <c r="B32" s="10"/>
-      <c r="C32" s="14" t="s">
+      <c r="C32" s="11" t="s">
         <v>85</v>
       </c>
       <c r="D32" s="9"/>
@@ -4731,257 +4790,257 @@
       <c r="G37" s="10"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A39" s="13" t="s">
+      <c r="A39" s="15" t="s">
         <v>96</v>
       </c>
-      <c r="B39" s="12"/>
-      <c r="C39" s="12"/>
-      <c r="D39" s="12"/>
-      <c r="E39" s="12"/>
-      <c r="F39" s="12"/>
-      <c r="G39" s="12"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="13"/>
+      <c r="F39" s="13"/>
+      <c r="G39" s="13"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A40" s="15" t="s">
+      <c r="A40" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="B40" s="12"/>
-      <c r="C40" s="12"/>
-      <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
-      <c r="F40" s="12"/>
-      <c r="G40" s="12"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="13"/>
+      <c r="F40" s="13"/>
+      <c r="G40" s="13"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A41" s="11" t="s">
+      <c r="A41" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="B41" s="12"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="12"/>
-      <c r="E41" s="12"/>
-      <c r="F41" s="12"/>
-      <c r="G41" s="12"/>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="13"/>
+      <c r="F41" s="13"/>
+      <c r="G41" s="13"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A42" s="11" t="s">
+      <c r="A42" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="B42" s="12"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="12"/>
-      <c r="G42" s="12"/>
+      <c r="B42" s="13"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="13"/>
+      <c r="F42" s="13"/>
+      <c r="G42" s="13"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A43" s="11" t="s">
+      <c r="A43" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="B43" s="12"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="12"/>
-      <c r="G43" s="12"/>
+      <c r="B43" s="13"/>
+      <c r="C43" s="13"/>
+      <c r="D43" s="13"/>
+      <c r="E43" s="13"/>
+      <c r="F43" s="13"/>
+      <c r="G43" s="13"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A44" s="11" t="s">
+      <c r="A44" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="B44" s="12"/>
-      <c r="C44" s="12"/>
-      <c r="D44" s="12"/>
-      <c r="E44" s="12"/>
-      <c r="F44" s="12"/>
-      <c r="G44" s="12"/>
+      <c r="B44" s="13"/>
+      <c r="C44" s="13"/>
+      <c r="D44" s="13"/>
+      <c r="E44" s="13"/>
+      <c r="F44" s="13"/>
+      <c r="G44" s="13"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A45" s="15" t="s">
+      <c r="A45" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="B45" s="12"/>
-      <c r="C45" s="12"/>
-      <c r="D45" s="12"/>
-      <c r="E45" s="12"/>
-      <c r="F45" s="12"/>
-      <c r="G45" s="12"/>
+      <c r="B45" s="13"/>
+      <c r="C45" s="13"/>
+      <c r="D45" s="13"/>
+      <c r="E45" s="13"/>
+      <c r="F45" s="13"/>
+      <c r="G45" s="13"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A46" s="11" t="s">
+      <c r="A46" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="B46" s="12"/>
-      <c r="C46" s="12"/>
-      <c r="D46" s="12"/>
-      <c r="E46" s="12"/>
-      <c r="F46" s="12"/>
-      <c r="G46" s="12"/>
+      <c r="B46" s="13"/>
+      <c r="C46" s="13"/>
+      <c r="D46" s="13"/>
+      <c r="E46" s="13"/>
+      <c r="F46" s="13"/>
+      <c r="G46" s="13"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A47" s="11" t="s">
+      <c r="A47" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="B47" s="12"/>
-      <c r="C47" s="12"/>
-      <c r="D47" s="12"/>
-      <c r="E47" s="12"/>
-      <c r="F47" s="12"/>
-      <c r="G47" s="12"/>
+      <c r="B47" s="13"/>
+      <c r="C47" s="13"/>
+      <c r="D47" s="13"/>
+      <c r="E47" s="13"/>
+      <c r="F47" s="13"/>
+      <c r="G47" s="13"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A48" s="11" t="s">
+      <c r="A48" s="12" t="s">
         <v>104</v>
       </c>
-      <c r="B48" s="12"/>
-      <c r="C48" s="12"/>
-      <c r="D48" s="12"/>
-      <c r="E48" s="12"/>
-      <c r="F48" s="12"/>
-      <c r="G48" s="12"/>
+      <c r="B48" s="13"/>
+      <c r="C48" s="13"/>
+      <c r="D48" s="13"/>
+      <c r="E48" s="13"/>
+      <c r="F48" s="13"/>
+      <c r="G48" s="13"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A49" s="15" t="s">
+      <c r="A49" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="B49" s="12"/>
-      <c r="C49" s="12"/>
-      <c r="D49" s="12"/>
-      <c r="E49" s="12"/>
-      <c r="F49" s="12"/>
-      <c r="G49" s="12"/>
+      <c r="B49" s="13"/>
+      <c r="C49" s="13"/>
+      <c r="D49" s="13"/>
+      <c r="E49" s="13"/>
+      <c r="F49" s="13"/>
+      <c r="G49" s="13"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A50" s="11" t="s">
+      <c r="A50" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="B50" s="12"/>
-      <c r="C50" s="12"/>
-      <c r="D50" s="12"/>
-      <c r="E50" s="12"/>
-      <c r="F50" s="12"/>
-      <c r="G50" s="12"/>
+      <c r="B50" s="13"/>
+      <c r="C50" s="13"/>
+      <c r="D50" s="13"/>
+      <c r="E50" s="13"/>
+      <c r="F50" s="13"/>
+      <c r="G50" s="13"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A51" s="11" t="s">
+      <c r="A51" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="B51" s="12"/>
-      <c r="C51" s="12"/>
-      <c r="D51" s="12"/>
-      <c r="E51" s="12"/>
-      <c r="F51" s="12"/>
-      <c r="G51" s="12"/>
+      <c r="B51" s="13"/>
+      <c r="C51" s="13"/>
+      <c r="D51" s="13"/>
+      <c r="E51" s="13"/>
+      <c r="F51" s="13"/>
+      <c r="G51" s="13"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A52" s="11" t="s">
+      <c r="A52" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="B52" s="12"/>
-      <c r="C52" s="12"/>
-      <c r="D52" s="12"/>
-      <c r="E52" s="12"/>
-      <c r="F52" s="12"/>
-      <c r="G52" s="12"/>
+      <c r="B52" s="13"/>
+      <c r="C52" s="13"/>
+      <c r="D52" s="13"/>
+      <c r="E52" s="13"/>
+      <c r="F52" s="13"/>
+      <c r="G52" s="13"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A53" s="11" t="s">
+      <c r="A53" s="12" t="s">
         <v>109</v>
       </c>
-      <c r="B53" s="12"/>
-      <c r="C53" s="12"/>
-      <c r="D53" s="12"/>
-      <c r="E53" s="12"/>
-      <c r="F53" s="12"/>
-      <c r="G53" s="12"/>
+      <c r="B53" s="13"/>
+      <c r="C53" s="13"/>
+      <c r="D53" s="13"/>
+      <c r="E53" s="13"/>
+      <c r="F53" s="13"/>
+      <c r="G53" s="13"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A54" s="11" t="s">
+      <c r="A54" s="12" t="s">
         <v>110</v>
       </c>
-      <c r="B54" s="12"/>
-      <c r="C54" s="12"/>
-      <c r="D54" s="12"/>
-      <c r="E54" s="12"/>
-      <c r="F54" s="12"/>
-      <c r="G54" s="12"/>
+      <c r="B54" s="13"/>
+      <c r="C54" s="13"/>
+      <c r="D54" s="13"/>
+      <c r="E54" s="13"/>
+      <c r="F54" s="13"/>
+      <c r="G54" s="13"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A55" s="15" t="s">
+      <c r="A55" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="B55" s="12"/>
-      <c r="C55" s="12"/>
-      <c r="D55" s="12"/>
-      <c r="E55" s="12"/>
-      <c r="F55" s="12"/>
-      <c r="G55" s="12"/>
+      <c r="B55" s="13"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A56" s="11" t="s">
+      <c r="A56" s="12" t="s">
         <v>106</v>
       </c>
-      <c r="B56" s="12"/>
-      <c r="C56" s="12"/>
-      <c r="D56" s="12"/>
-      <c r="E56" s="12"/>
-      <c r="F56" s="12"/>
-      <c r="G56" s="12"/>
+      <c r="B56" s="13"/>
+      <c r="C56" s="13"/>
+      <c r="D56" s="13"/>
+      <c r="E56" s="13"/>
+      <c r="F56" s="13"/>
+      <c r="G56" s="13"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A57" s="11" t="s">
+      <c r="A57" s="12" t="s">
         <v>112</v>
       </c>
-      <c r="B57" s="12"/>
-      <c r="C57" s="12"/>
-      <c r="D57" s="12"/>
-      <c r="E57" s="12"/>
-      <c r="F57" s="12"/>
-      <c r="G57" s="12"/>
+      <c r="B57" s="13"/>
+      <c r="C57" s="13"/>
+      <c r="D57" s="13"/>
+      <c r="E57" s="13"/>
+      <c r="F57" s="13"/>
+      <c r="G57" s="13"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A58" s="11" t="s">
+      <c r="A58" s="12" t="s">
         <v>113</v>
       </c>
-      <c r="B58" s="12"/>
-      <c r="C58" s="12"/>
-      <c r="D58" s="12"/>
-      <c r="E58" s="12"/>
-      <c r="F58" s="12"/>
-      <c r="G58" s="12"/>
+      <c r="B58" s="13"/>
+      <c r="C58" s="13"/>
+      <c r="D58" s="13"/>
+      <c r="E58" s="13"/>
+      <c r="F58" s="13"/>
+      <c r="G58" s="13"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A59" s="11" t="s">
+      <c r="A59" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="B59" s="12"/>
-      <c r="C59" s="12"/>
-      <c r="D59" s="12"/>
-      <c r="E59" s="12"/>
-      <c r="F59" s="12"/>
-      <c r="G59" s="12"/>
+      <c r="B59" s="13"/>
+      <c r="C59" s="13"/>
+      <c r="D59" s="13"/>
+      <c r="E59" s="13"/>
+      <c r="F59" s="13"/>
+      <c r="G59" s="13"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A61" s="13" t="s">
+      <c r="A61" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="B61" s="12"/>
-      <c r="C61" s="12"/>
-      <c r="D61" s="12"/>
-      <c r="E61" s="12"/>
-      <c r="F61" s="12"/>
-      <c r="G61" s="12"/>
+      <c r="B61" s="13"/>
+      <c r="C61" s="13"/>
+      <c r="D61" s="13"/>
+      <c r="E61" s="13"/>
+      <c r="F61" s="13"/>
+      <c r="G61" s="13"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A62" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B62" s="14" t="s">
+      <c r="B62" s="11" t="s">
         <v>117</v>
       </c>
       <c r="C62" s="9"/>
       <c r="D62" s="10"/>
-      <c r="E62" s="14" t="s">
+      <c r="E62" s="11" t="s">
         <v>118</v>
       </c>
       <c r="F62" s="9"/>
@@ -5078,21 +5137,21 @@
       <c r="G68" s="10"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A70" s="13" t="s">
+      <c r="A70" s="15" t="s">
         <v>137</v>
       </c>
-      <c r="B70" s="12"/>
-      <c r="C70" s="12"/>
-      <c r="D70" s="12"/>
-      <c r="E70" s="12"/>
-      <c r="F70" s="12"/>
-      <c r="G70" s="12"/>
+      <c r="B70" s="13"/>
+      <c r="C70" s="13"/>
+      <c r="D70" s="13"/>
+      <c r="E70" s="13"/>
+      <c r="F70" s="13"/>
+      <c r="G70" s="13"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="B71" s="14" t="s">
+      <c r="B71" s="11" t="s">
         <v>23</v>
       </c>
       <c r="C71" s="10"/>
@@ -5102,7 +5161,7 @@
       <c r="E71" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="F71" s="14" t="s">
+      <c r="F71" s="11" t="s">
         <v>139</v>
       </c>
       <c r="G71" s="10"/>
@@ -5298,40 +5357,40 @@
       <c r="G81" s="10"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A82" s="16" t="s">
+      <c r="A82" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="B82" s="12"/>
-      <c r="C82" s="12"/>
-      <c r="D82" s="12"/>
-      <c r="E82" s="12"/>
-      <c r="F82" s="12"/>
-      <c r="G82" s="12"/>
+      <c r="B82" s="13"/>
+      <c r="C82" s="13"/>
+      <c r="D82" s="13"/>
+      <c r="E82" s="13"/>
+      <c r="F82" s="13"/>
+      <c r="G82" s="13"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A84" s="13" t="s">
+      <c r="A84" s="15" t="s">
         <v>181</v>
       </c>
-      <c r="B84" s="12"/>
-      <c r="C84" s="12"/>
-      <c r="D84" s="12"/>
-      <c r="E84" s="12"/>
-      <c r="F84" s="12"/>
-      <c r="G84" s="12"/>
+      <c r="B84" s="13"/>
+      <c r="C84" s="13"/>
+      <c r="D84" s="13"/>
+      <c r="E84" s="13"/>
+      <c r="F84" s="13"/>
+      <c r="G84" s="13"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A85" s="14" t="s">
+      <c r="A85" s="11" t="s">
         <v>46</v>
       </c>
       <c r="B85" s="10"/>
       <c r="C85" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="D85" s="14" t="s">
+      <c r="D85" s="11" t="s">
         <v>183</v>
       </c>
       <c r="E85" s="10"/>
-      <c r="F85" s="14" t="s">
+      <c r="F85" s="11" t="s">
         <v>184</v>
       </c>
       <c r="G85" s="10"/>
@@ -5439,33 +5498,33 @@
       <c r="G91" s="10"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A92" s="16" t="s">
+      <c r="A92" s="17" t="s">
         <v>206</v>
       </c>
-      <c r="B92" s="12"/>
-      <c r="C92" s="12"/>
-      <c r="D92" s="12"/>
-      <c r="E92" s="12"/>
-      <c r="F92" s="12"/>
-      <c r="G92" s="12"/>
+      <c r="B92" s="13"/>
+      <c r="C92" s="13"/>
+      <c r="D92" s="13"/>
+      <c r="E92" s="13"/>
+      <c r="F92" s="13"/>
+      <c r="G92" s="13"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A94" s="13" t="s">
+      <c r="A94" s="15" t="s">
         <v>207</v>
       </c>
-      <c r="B94" s="12"/>
-      <c r="C94" s="12"/>
-      <c r="D94" s="12"/>
-      <c r="E94" s="12"/>
-      <c r="F94" s="12"/>
-      <c r="G94" s="12"/>
+      <c r="B94" s="13"/>
+      <c r="C94" s="13"/>
+      <c r="D94" s="13"/>
+      <c r="E94" s="13"/>
+      <c r="F94" s="13"/>
+      <c r="G94" s="13"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A95" s="14" t="s">
+      <c r="A95" s="11" t="s">
         <v>208</v>
       </c>
       <c r="B95" s="10"/>
-      <c r="C95" s="14" t="s">
+      <c r="C95" s="11" t="s">
         <v>209</v>
       </c>
       <c r="D95" s="9"/>
@@ -5513,35 +5572,35 @@
       <c r="G98" s="10"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A99" s="16" t="s">
+      <c r="A99" s="17" t="s">
         <v>216</v>
       </c>
-      <c r="B99" s="12"/>
-      <c r="C99" s="12"/>
-      <c r="D99" s="12"/>
-      <c r="E99" s="12"/>
-      <c r="F99" s="12"/>
-      <c r="G99" s="12"/>
+      <c r="B99" s="13"/>
+      <c r="C99" s="13"/>
+      <c r="D99" s="13"/>
+      <c r="E99" s="13"/>
+      <c r="F99" s="13"/>
+      <c r="G99" s="13"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A101" s="13" t="s">
+      <c r="A101" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="B101" s="12"/>
-      <c r="C101" s="12"/>
-      <c r="D101" s="12"/>
-      <c r="E101" s="12"/>
-      <c r="F101" s="12"/>
-      <c r="G101" s="12"/>
+      <c r="B101" s="13"/>
+      <c r="C101" s="13"/>
+      <c r="D101" s="13"/>
+      <c r="E101" s="13"/>
+      <c r="F101" s="13"/>
+      <c r="G101" s="13"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A102" s="14" t="s">
+      <c r="A102" s="11" t="s">
         <v>218</v>
       </c>
       <c r="B102" s="9"/>
       <c r="C102" s="9"/>
       <c r="D102" s="10"/>
-      <c r="E102" s="14" t="s">
+      <c r="E102" s="11" t="s">
         <v>219</v>
       </c>
       <c r="F102" s="9"/>
@@ -5665,23 +5724,23 @@
       <c r="G111" s="10"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A113" s="13" t="s">
+      <c r="A113" s="15" t="s">
         <v>238</v>
       </c>
-      <c r="B113" s="12"/>
-      <c r="C113" s="12"/>
-      <c r="D113" s="12"/>
-      <c r="E113" s="12"/>
-      <c r="F113" s="12"/>
-      <c r="G113" s="12"/>
+      <c r="B113" s="13"/>
+      <c r="C113" s="13"/>
+      <c r="D113" s="13"/>
+      <c r="E113" s="13"/>
+      <c r="F113" s="13"/>
+      <c r="G113" s="13"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="A114" s="14" t="s">
+      <c r="A114" s="11" t="s">
         <v>239</v>
       </c>
       <c r="B114" s="9"/>
       <c r="C114" s="10"/>
-      <c r="D114" s="14" t="s">
+      <c r="D114" s="11" t="s">
         <v>240</v>
       </c>
       <c r="E114" s="9"/>
@@ -5768,28 +5827,135 @@
     </row>
   </sheetData>
   <mergeCells count="177">
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C95:G95"/>
-    <mergeCell ref="A46:G46"/>
-    <mergeCell ref="B74:C74"/>
-    <mergeCell ref="A105:D105"/>
-    <mergeCell ref="B66:D66"/>
-    <mergeCell ref="F77:G77"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="C97:G97"/>
-    <mergeCell ref="A19:G19"/>
-    <mergeCell ref="A28:G28"/>
-    <mergeCell ref="B68:D68"/>
-    <mergeCell ref="E104:G104"/>
-    <mergeCell ref="A43:G43"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A50:G50"/>
-    <mergeCell ref="B63:D63"/>
-    <mergeCell ref="B72:C72"/>
-    <mergeCell ref="A85:B85"/>
-    <mergeCell ref="D86:E86"/>
-    <mergeCell ref="E65:G65"/>
-    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="D120:G120"/>
+    <mergeCell ref="A21:G21"/>
+    <mergeCell ref="A52:G52"/>
+    <mergeCell ref="A61:G61"/>
+    <mergeCell ref="A111:D111"/>
+    <mergeCell ref="D116:G116"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="A87:B87"/>
+    <mergeCell ref="C96:G96"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="E107:G107"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="B76:C76"/>
+    <mergeCell ref="E103:G103"/>
+    <mergeCell ref="D85:E85"/>
+    <mergeCell ref="F85:G85"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="F79:G79"/>
+    <mergeCell ref="A98:B98"/>
+    <mergeCell ref="A47:G47"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A58:G58"/>
+    <mergeCell ref="A106:D106"/>
+    <mergeCell ref="F78:G78"/>
+    <mergeCell ref="F71:G71"/>
+    <mergeCell ref="A32:B32"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="E105:G105"/>
+    <mergeCell ref="E102:G102"/>
+    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="C36:G36"/>
+    <mergeCell ref="E63:G63"/>
+    <mergeCell ref="A107:D107"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A45:G45"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A118:C118"/>
+    <mergeCell ref="A25:G25"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="D87:E87"/>
+    <mergeCell ref="A70:G70"/>
+    <mergeCell ref="F87:G87"/>
+    <mergeCell ref="E106:G106"/>
+    <mergeCell ref="A22:G22"/>
+    <mergeCell ref="C33:G33"/>
+    <mergeCell ref="A117:C117"/>
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="C35:G35"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="A55:G55"/>
+    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="E66:G66"/>
+    <mergeCell ref="F81:G81"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A84:G84"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="D89:E89"/>
+    <mergeCell ref="E68:G68"/>
+    <mergeCell ref="A99:G99"/>
+    <mergeCell ref="A119:C119"/>
+    <mergeCell ref="A51:G51"/>
+    <mergeCell ref="F73:G73"/>
+    <mergeCell ref="A110:D110"/>
+    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="A92:G92"/>
+    <mergeCell ref="A101:G101"/>
+    <mergeCell ref="A82:G82"/>
+    <mergeCell ref="F75:G75"/>
+    <mergeCell ref="A36:B36"/>
+    <mergeCell ref="D114:G114"/>
+    <mergeCell ref="A88:B88"/>
+    <mergeCell ref="B67:D67"/>
+    <mergeCell ref="A48:G48"/>
+    <mergeCell ref="D117:G117"/>
+    <mergeCell ref="B71:C71"/>
+    <mergeCell ref="B80:C80"/>
+    <mergeCell ref="C32:G32"/>
+    <mergeCell ref="A13:B13"/>
+    <mergeCell ref="A120:C120"/>
+    <mergeCell ref="F74:G74"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="E111:G111"/>
+    <mergeCell ref="E108:G108"/>
+    <mergeCell ref="A90:B90"/>
+    <mergeCell ref="E110:G110"/>
+    <mergeCell ref="A104:D104"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="B79:C79"/>
+    <mergeCell ref="A54:G54"/>
+    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="A94:G94"/>
+    <mergeCell ref="D88:E88"/>
+    <mergeCell ref="A56:G56"/>
+    <mergeCell ref="B78:C78"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="E62:G62"/>
+    <mergeCell ref="F72:G72"/>
+    <mergeCell ref="A91:B91"/>
+    <mergeCell ref="F86:G86"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="E64:G64"/>
+    <mergeCell ref="A108:D108"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="F88:G88"/>
+    <mergeCell ref="C34:G34"/>
+    <mergeCell ref="A57:G57"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="A23:G23"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="B64:D64"/>
+    <mergeCell ref="A59:G59"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="B81:C81"/>
+    <mergeCell ref="A11:B11"/>
+    <mergeCell ref="D90:E90"/>
+    <mergeCell ref="A102:D102"/>
+    <mergeCell ref="F90:G90"/>
+    <mergeCell ref="B62:D62"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="C10:G10"/>
     <mergeCell ref="D119:G119"/>
     <mergeCell ref="F76:G76"/>
     <mergeCell ref="A37:B37"/>
@@ -5814,137 +5980,30 @@
     <mergeCell ref="E67:G67"/>
     <mergeCell ref="A96:B96"/>
     <mergeCell ref="B73:C73"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="E64:G64"/>
-    <mergeCell ref="A108:D108"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A42:G42"/>
-    <mergeCell ref="F88:G88"/>
-    <mergeCell ref="C34:G34"/>
-    <mergeCell ref="A57:G57"/>
-    <mergeCell ref="A39:G39"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="A23:G23"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="B64:D64"/>
-    <mergeCell ref="A59:G59"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="B81:C81"/>
-    <mergeCell ref="A11:B11"/>
-    <mergeCell ref="D90:E90"/>
-    <mergeCell ref="A102:D102"/>
-    <mergeCell ref="F90:G90"/>
-    <mergeCell ref="B62:D62"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="C10:G10"/>
-    <mergeCell ref="A120:C120"/>
-    <mergeCell ref="F74:G74"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="E111:G111"/>
-    <mergeCell ref="E108:G108"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="E110:G110"/>
-    <mergeCell ref="A104:D104"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="B79:C79"/>
-    <mergeCell ref="A54:G54"/>
-    <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A94:G94"/>
-    <mergeCell ref="D88:E88"/>
-    <mergeCell ref="A56:G56"/>
-    <mergeCell ref="B78:C78"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A31:G31"/>
-    <mergeCell ref="E62:G62"/>
-    <mergeCell ref="F72:G72"/>
-    <mergeCell ref="A91:B91"/>
-    <mergeCell ref="F86:G86"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="D89:E89"/>
-    <mergeCell ref="E68:G68"/>
-    <mergeCell ref="A99:G99"/>
-    <mergeCell ref="A119:C119"/>
-    <mergeCell ref="A51:G51"/>
-    <mergeCell ref="F73:G73"/>
-    <mergeCell ref="A110:D110"/>
-    <mergeCell ref="A86:B86"/>
-    <mergeCell ref="A92:G92"/>
-    <mergeCell ref="A101:G101"/>
-    <mergeCell ref="A82:G82"/>
-    <mergeCell ref="F75:G75"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="D114:G114"/>
-    <mergeCell ref="A88:B88"/>
-    <mergeCell ref="B67:D67"/>
-    <mergeCell ref="A48:G48"/>
-    <mergeCell ref="D117:G117"/>
-    <mergeCell ref="B71:C71"/>
-    <mergeCell ref="B80:C80"/>
-    <mergeCell ref="C32:G32"/>
-    <mergeCell ref="A13:B13"/>
-    <mergeCell ref="A107:D107"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="A20:G20"/>
-    <mergeCell ref="A118:C118"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A8:B8"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="A70:G70"/>
-    <mergeCell ref="F87:G87"/>
-    <mergeCell ref="E106:G106"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="C33:G33"/>
-    <mergeCell ref="A117:C117"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="C35:G35"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="A55:G55"/>
-    <mergeCell ref="A26:G26"/>
-    <mergeCell ref="E66:G66"/>
-    <mergeCell ref="F81:G81"/>
-    <mergeCell ref="A12:B12"/>
-    <mergeCell ref="A84:G84"/>
-    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C95:G95"/>
+    <mergeCell ref="A46:G46"/>
+    <mergeCell ref="B74:C74"/>
+    <mergeCell ref="A105:D105"/>
+    <mergeCell ref="B66:D66"/>
+    <mergeCell ref="F77:G77"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="C97:G97"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="B68:D68"/>
+    <mergeCell ref="E104:G104"/>
+    <mergeCell ref="A43:G43"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A50:G50"/>
+    <mergeCell ref="B63:D63"/>
+    <mergeCell ref="B72:C72"/>
+    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="D86:E86"/>
+    <mergeCell ref="E65:G65"/>
+    <mergeCell ref="A14:B14"/>
     <mergeCell ref="A44:G44"/>
     <mergeCell ref="B77:C77"/>
-    <mergeCell ref="F71:G71"/>
-    <mergeCell ref="A32:B32"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="A16:B16"/>
-    <mergeCell ref="E105:G105"/>
-    <mergeCell ref="E102:G102"/>
-    <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C36:G36"/>
-    <mergeCell ref="E63:G63"/>
-    <mergeCell ref="D120:G120"/>
-    <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A52:G52"/>
-    <mergeCell ref="A61:G61"/>
-    <mergeCell ref="A111:D111"/>
-    <mergeCell ref="D116:G116"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="A87:B87"/>
-    <mergeCell ref="C96:G96"/>
-    <mergeCell ref="A18:G18"/>
-    <mergeCell ref="E107:G107"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="B76:C76"/>
-    <mergeCell ref="E103:G103"/>
-    <mergeCell ref="D85:E85"/>
-    <mergeCell ref="F85:G85"/>
-    <mergeCell ref="A89:B89"/>
-    <mergeCell ref="F79:G79"/>
-    <mergeCell ref="A98:B98"/>
-    <mergeCell ref="A47:G47"/>
-    <mergeCell ref="A29:G29"/>
-    <mergeCell ref="A58:G58"/>
-    <mergeCell ref="A106:D106"/>
-    <mergeCell ref="F78:G78"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5953,7 +6012,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D34309FD-96CC-4190-83BD-5F2A8AEA44E3}">
-  <dimension ref="B2:G13"/>
+  <dimension ref="A2:K28"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="3" max="3" width="18.1640625" bestFit="1" customWidth="1"/>
@@ -5962,12 +6021,12 @@
     <col min="7" max="7" width="11.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" s="6" t="s">
         <v>253</v>
       </c>
@@ -5987,7 +6046,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="4" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="4" t="s">
         <v>294</v>
       </c>
@@ -6007,7 +6066,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="4" t="s">
         <v>295</v>
       </c>
@@ -6027,7 +6086,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="4" t="s">
         <v>295</v>
       </c>
@@ -6047,7 +6106,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="4" t="s">
         <v>295</v>
       </c>
@@ -6067,7 +6126,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="8" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="4" t="s">
         <v>296</v>
       </c>
@@ -6087,7 +6146,7 @@
         <v>287</v>
       </c>
     </row>
-    <row r="9" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="4" t="s">
         <v>297</v>
       </c>
@@ -6107,7 +6166,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="10" spans="2:7" ht="36" x14ac:dyDescent="0.55000000000000004">
+    <row r="10" spans="1:11" ht="36" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="4" t="s">
         <v>297</v>
       </c>
@@ -6127,7 +6186,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="11" spans="2:7" x14ac:dyDescent="0.55000000000000004">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="4" t="s">
         <v>298</v>
       </c>
@@ -6147,10 +6206,215 @@
         <v>299</v>
       </c>
     </row>
-    <row r="13" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B13" t="s">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A13" s="19"/>
+      <c r="B13" s="19" t="s">
         <v>300</v>
       </c>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="19"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="19"/>
+      <c r="I14" s="19"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19"/>
+      <c r="J16" s="19"/>
+      <c r="K16" s="19"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="19"/>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19"/>
+      <c r="K17" s="19"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+      <c r="H18" s="19"/>
+      <c r="I18" s="19"/>
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A19" s="19"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+      <c r="H19" s="19"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="19"/>
+      <c r="K19" s="19"/>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A20" s="19"/>
+      <c r="B20" s="19"/>
+      <c r="C20" s="19"/>
+      <c r="D20" s="19"/>
+      <c r="E20" s="19"/>
+      <c r="F20" s="19"/>
+      <c r="G20" s="19"/>
+      <c r="H20" s="19"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="19"/>
+      <c r="K20" s="19"/>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A21" s="19"/>
+      <c r="B21" s="19"/>
+      <c r="C21" s="19"/>
+      <c r="D21" s="19"/>
+      <c r="E21" s="19"/>
+      <c r="F21" s="19"/>
+      <c r="G21" s="19"/>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19"/>
+      <c r="J21" s="19"/>
+      <c r="K21" s="19"/>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A22" s="19"/>
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="19"/>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A23" s="19"/>
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A24" s="19"/>
+      <c r="B24" s="19"/>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+      <c r="H24" s="19"/>
+      <c r="I24" s="19"/>
+      <c r="J24" s="19"/>
+      <c r="K24" s="19"/>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A25" s="19"/>
+      <c r="B25" s="19"/>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="19"/>
+      <c r="I25" s="19"/>
+      <c r="J25" s="19"/>
+      <c r="K25" s="19"/>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A26" s="19"/>
+      <c r="B26" s="19"/>
+      <c r="C26" s="19"/>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19"/>
+      <c r="K26" s="19"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A27" s="19"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+      <c r="H27" s="19"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19"/>
+      <c r="K27" s="19"/>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.55000000000000004">
+      <c r="A28" s="19"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="19"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -6173,7 +6437,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B1" s="11" t="s">
+      <c r="B1" s="12" t="s">
         <v>541</v>
       </c>
       <c r="C1" s="18"/>
@@ -6183,7 +6447,7 @@
       <c r="G1" s="18"/>
     </row>
     <row r="2" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="12" t="s">
         <v>542</v>
       </c>
       <c r="C2" s="18"/>
@@ -6193,7 +6457,7 @@
       <c r="G2" s="18"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="12" t="s">
         <v>301</v>
       </c>
       <c r="C4" s="18"/>
@@ -6206,7 +6470,7 @@
       <c r="B5" s="7" t="s">
         <v>302</v>
       </c>
-      <c r="C5" s="11" t="s">
+      <c r="C5" s="12" t="s">
         <v>303</v>
       </c>
       <c r="D5" s="18"/>
@@ -6218,7 +6482,7 @@
       <c r="B6" s="7" t="s">
         <v>304</v>
       </c>
-      <c r="C6" s="11" t="s">
+      <c r="C6" s="12" t="s">
         <v>305</v>
       </c>
       <c r="D6" s="18"/>
@@ -6230,7 +6494,7 @@
       <c r="B7" s="7" t="s">
         <v>306</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="12" t="s">
         <v>307</v>
       </c>
       <c r="D7" s="18"/>
@@ -6242,7 +6506,7 @@
       <c r="B8" s="7" t="s">
         <v>308</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="12" t="s">
         <v>309</v>
       </c>
       <c r="D8" s="18"/>
@@ -6254,7 +6518,7 @@
       <c r="B9" s="7" t="s">
         <v>310</v>
       </c>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="12" t="s">
         <v>311</v>
       </c>
       <c r="D9" s="18"/>
@@ -6266,7 +6530,7 @@
       <c r="B10" s="7" t="s">
         <v>312</v>
       </c>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="12" t="s">
         <v>313</v>
       </c>
       <c r="D10" s="18"/>
@@ -6278,7 +6542,7 @@
       <c r="B11" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="12" t="s">
         <v>315</v>
       </c>
       <c r="D11" s="18"/>
@@ -6290,7 +6554,7 @@
       <c r="B12" s="7" t="s">
         <v>316</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="12" t="s">
         <v>317</v>
       </c>
       <c r="D12" s="18"/>
@@ -6302,7 +6566,7 @@
       <c r="B13" s="7" t="s">
         <v>514</v>
       </c>
-      <c r="C13" s="11" t="s">
+      <c r="C13" s="12" t="s">
         <v>515</v>
       </c>
       <c r="D13" s="18"/>
@@ -6314,7 +6578,7 @@
       <c r="B14" s="7" t="s">
         <v>516</v>
       </c>
-      <c r="C14" s="11" t="s">
+      <c r="C14" s="12" t="s">
         <v>517</v>
       </c>
       <c r="D14" s="18"/>
@@ -6326,7 +6590,7 @@
       <c r="B15" s="7" t="s">
         <v>318</v>
       </c>
-      <c r="C15" s="11" t="s">
+      <c r="C15" s="12" t="s">
         <v>319</v>
       </c>
       <c r="D15" s="18"/>
@@ -6338,7 +6602,7 @@
       <c r="B16" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="12" t="s">
         <v>518</v>
       </c>
       <c r="D16" s="18"/>
@@ -6350,7 +6614,7 @@
       <c r="B17" s="7" t="s">
         <v>519</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="12" t="s">
         <v>520</v>
       </c>
       <c r="D17" s="18"/>
@@ -6362,7 +6626,7 @@
       <c r="B18" s="7" t="s">
         <v>521</v>
       </c>
-      <c r="C18" s="11" t="s">
+      <c r="C18" s="12" t="s">
         <v>522</v>
       </c>
       <c r="D18" s="18"/>
@@ -6374,7 +6638,7 @@
       <c r="B19" s="7" t="s">
         <v>320</v>
       </c>
-      <c r="C19" s="11" t="s">
+      <c r="C19" s="12" t="s">
         <v>523</v>
       </c>
       <c r="D19" s="18"/>
@@ -6386,7 +6650,7 @@
       <c r="B20" s="7" t="s">
         <v>321</v>
       </c>
-      <c r="C20" s="11" t="s">
+      <c r="C20" s="12" t="s">
         <v>322</v>
       </c>
       <c r="D20" s="18"/>
@@ -6395,7 +6659,7 @@
       <c r="G20" s="18"/>
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B22" s="11" t="s">
+      <c r="B22" s="12" t="s">
         <v>323</v>
       </c>
       <c r="C22" s="18"/>
@@ -6625,7 +6889,7 @@
       </c>
     </row>
     <row r="34" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B34" s="11" t="s">
+      <c r="B34" s="12" t="s">
         <v>543</v>
       </c>
       <c r="C34" s="18"/>
@@ -6635,7 +6899,7 @@
       <c r="G34" s="18"/>
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B35" s="11" t="s">
+      <c r="B35" s="12" t="s">
         <v>526</v>
       </c>
       <c r="C35" s="18"/>
@@ -6645,7 +6909,7 @@
       <c r="G35" s="18"/>
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B36" s="11" t="s">
+      <c r="B36" s="12" t="s">
         <v>544</v>
       </c>
       <c r="C36" s="18"/>
@@ -6655,7 +6919,7 @@
       <c r="G36" s="18"/>
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B38" s="11" t="s">
+      <c r="B38" s="12" t="s">
         <v>367</v>
       </c>
       <c r="C38" s="18"/>
@@ -6665,7 +6929,7 @@
       <c r="G38" s="18"/>
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B40" s="11" t="s">
+      <c r="B40" s="12" t="s">
         <v>368</v>
       </c>
       <c r="C40" s="18"/>
@@ -6678,7 +6942,7 @@
       <c r="B41" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="C41" s="11" t="s">
+      <c r="C41" s="12" t="s">
         <v>369</v>
       </c>
       <c r="D41" s="18"/>
@@ -6687,7 +6951,7 @@
       <c r="G41" s="18"/>
     </row>
     <row r="42" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B42" s="11" t="s">
+      <c r="B42" s="12" t="s">
         <v>370</v>
       </c>
       <c r="C42" s="18"/>
@@ -6731,7 +6995,7 @@
       </c>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B45" s="11" t="s">
+      <c r="B45" s="12" t="s">
         <v>379</v>
       </c>
       <c r="C45" s="18"/>
@@ -6744,7 +7008,7 @@
       <c r="B46" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="C46" s="11" t="s">
+      <c r="C46" s="12" t="s">
         <v>381</v>
       </c>
       <c r="D46" s="18"/>
@@ -6863,7 +7127,7 @@
       </c>
     </row>
     <row r="57" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B57" s="11" t="s">
+      <c r="B57" s="12" t="s">
         <v>403</v>
       </c>
       <c r="C57" s="18"/>
@@ -6873,7 +7137,7 @@
       <c r="G57" s="18"/>
     </row>
     <row r="58" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B58" s="11" t="s">
+      <c r="B58" s="12" t="s">
         <v>529</v>
       </c>
       <c r="C58" s="18"/>
@@ -6886,7 +7150,7 @@
       <c r="B59" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="C59" s="11" t="s">
+      <c r="C59" s="12" t="s">
         <v>530</v>
       </c>
       <c r="D59" s="18"/>
@@ -6895,7 +7159,7 @@
       <c r="G59" s="18"/>
     </row>
     <row r="61" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B61" s="11" t="s">
+      <c r="B61" s="12" t="s">
         <v>405</v>
       </c>
       <c r="C61" s="18"/>
@@ -6908,7 +7172,7 @@
       <c r="B62" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="C62" s="11" t="s">
+      <c r="C62" s="12" t="s">
         <v>333</v>
       </c>
       <c r="D62" s="18"/>
@@ -6917,7 +7181,7 @@
       <c r="G62" s="18"/>
     </row>
     <row r="63" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B63" s="11" t="s">
+      <c r="B63" s="12" t="s">
         <v>370</v>
       </c>
       <c r="C63" s="18"/>
@@ -6961,7 +7225,7 @@
       </c>
     </row>
     <row r="66" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B66" s="11" t="s">
+      <c r="B66" s="12" t="s">
         <v>379</v>
       </c>
       <c r="C66" s="18"/>
@@ -6974,7 +7238,7 @@
       <c r="B67" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="C67" s="11" t="s">
+      <c r="C67" s="12" t="s">
         <v>381</v>
       </c>
       <c r="D67" s="18"/>
@@ -7027,7 +7291,7 @@
       </c>
     </row>
     <row r="72" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B72" s="11" t="s">
+      <c r="B72" s="12" t="s">
         <v>403</v>
       </c>
       <c r="C72" s="18"/>
@@ -7062,7 +7326,7 @@
       <c r="B75" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="C75" s="11" t="s">
+      <c r="C75" s="12" t="s">
         <v>419</v>
       </c>
       <c r="D75" s="18"/>
@@ -7074,7 +7338,7 @@
       <c r="B76" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C76" s="11" t="s">
+      <c r="C76" s="12" t="s">
         <v>531</v>
       </c>
       <c r="D76" s="18"/>
@@ -7083,7 +7347,7 @@
       <c r="G76" s="18"/>
     </row>
     <row r="78" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B78" s="11" t="s">
+      <c r="B78" s="12" t="s">
         <v>420</v>
       </c>
       <c r="C78" s="18"/>
@@ -7096,7 +7360,7 @@
       <c r="B79" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="C79" s="11" t="s">
+      <c r="C79" s="12" t="s">
         <v>421</v>
       </c>
       <c r="D79" s="18"/>
@@ -7105,7 +7369,7 @@
       <c r="G79" s="18"/>
     </row>
     <row r="80" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B80" s="11" t="s">
+      <c r="B80" s="12" t="s">
         <v>370</v>
       </c>
       <c r="C80" s="18"/>
@@ -7149,7 +7413,7 @@
       </c>
     </row>
     <row r="83" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B83" s="11" t="s">
+      <c r="B83" s="12" t="s">
         <v>379</v>
       </c>
       <c r="C83" s="18"/>
@@ -7162,7 +7426,7 @@
       <c r="B84" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="C84" s="11" t="s">
+      <c r="C84" s="12" t="s">
         <v>426</v>
       </c>
       <c r="D84" s="18"/>
@@ -7237,7 +7501,7 @@
       </c>
     </row>
     <row r="91" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B91" s="11" t="s">
+      <c r="B91" s="12" t="s">
         <v>403</v>
       </c>
       <c r="C91" s="18"/>
@@ -7305,7 +7569,7 @@
       <c r="B97" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="C97" s="11" t="s">
+      <c r="C97" s="12" t="s">
         <v>441</v>
       </c>
       <c r="D97" s="18"/>
@@ -7317,7 +7581,7 @@
       <c r="B98" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C98" s="11" t="s">
+      <c r="C98" s="12" t="s">
         <v>532</v>
       </c>
       <c r="D98" s="18"/>
@@ -7326,7 +7590,7 @@
       <c r="G98" s="18"/>
     </row>
     <row r="100" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B100" s="11" t="s">
+      <c r="B100" s="12" t="s">
         <v>442</v>
       </c>
       <c r="C100" s="18"/>
@@ -7339,7 +7603,7 @@
       <c r="B101" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="C101" s="11" t="s">
+      <c r="C101" s="12" t="s">
         <v>443</v>
       </c>
       <c r="D101" s="18"/>
@@ -7348,7 +7612,7 @@
       <c r="G101" s="18"/>
     </row>
     <row r="102" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B102" s="11" t="s">
+      <c r="B102" s="12" t="s">
         <v>370</v>
       </c>
       <c r="C102" s="18"/>
@@ -7358,7 +7622,7 @@
       <c r="G102" s="18"/>
     </row>
     <row r="103" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B103" s="11" t="s">
+      <c r="B103" s="12" t="s">
         <v>444</v>
       </c>
       <c r="C103" s="18"/>
@@ -7368,7 +7632,7 @@
       <c r="G103" s="18"/>
     </row>
     <row r="104" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B104" s="11" t="s">
+      <c r="B104" s="12" t="s">
         <v>379</v>
       </c>
       <c r="C104" s="18"/>
@@ -7381,7 +7645,7 @@
       <c r="B105" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="C105" s="11" t="s">
+      <c r="C105" s="12" t="s">
         <v>381</v>
       </c>
       <c r="D105" s="18"/>
@@ -7478,7 +7742,7 @@
       </c>
     </row>
     <row r="114" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B114" s="11" t="s">
+      <c r="B114" s="12" t="s">
         <v>403</v>
       </c>
       <c r="C114" s="18"/>
@@ -7488,7 +7752,7 @@
       <c r="G114" s="18"/>
     </row>
     <row r="115" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B115" s="11" t="s">
+      <c r="B115" s="12" t="s">
         <v>529</v>
       </c>
       <c r="C115" s="18"/>
@@ -7501,7 +7765,7 @@
       <c r="B116" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="C116" s="11" t="s">
+      <c r="C116" s="12" t="s">
         <v>449</v>
       </c>
       <c r="D116" s="18"/>
@@ -7510,7 +7774,7 @@
       <c r="G116" s="18"/>
     </row>
     <row r="118" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B118" s="11" t="s">
+      <c r="B118" s="12" t="s">
         <v>450</v>
       </c>
       <c r="C118" s="18"/>
@@ -7523,7 +7787,7 @@
       <c r="B119" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="C119" s="11" t="s">
+      <c r="C119" s="12" t="s">
         <v>451</v>
       </c>
       <c r="D119" s="18"/>
@@ -7532,7 +7796,7 @@
       <c r="G119" s="18"/>
     </row>
     <row r="120" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B120" s="11" t="s">
+      <c r="B120" s="12" t="s">
         <v>370</v>
       </c>
       <c r="C120" s="18"/>
@@ -7576,7 +7840,7 @@
       </c>
     </row>
     <row r="123" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B123" s="11" t="s">
+      <c r="B123" s="12" t="s">
         <v>379</v>
       </c>
       <c r="C123" s="18"/>
@@ -7589,7 +7853,7 @@
       <c r="B124" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="C124" s="11" t="s">
+      <c r="C124" s="12" t="s">
         <v>452</v>
       </c>
       <c r="D124" s="18"/>
@@ -7598,7 +7862,7 @@
       <c r="G124" s="18"/>
     </row>
     <row r="125" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B125" s="11" t="s">
+      <c r="B125" s="12" t="s">
         <v>453</v>
       </c>
       <c r="C125" s="18"/>
@@ -7608,7 +7872,7 @@
       <c r="G125" s="18"/>
     </row>
     <row r="126" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B126" s="11" t="s">
+      <c r="B126" s="12" t="s">
         <v>403</v>
       </c>
       <c r="C126" s="18"/>
@@ -7665,7 +7929,7 @@
       <c r="B131" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="C131" s="11" t="s">
+      <c r="C131" s="12" t="s">
         <v>461</v>
       </c>
       <c r="D131" s="18"/>
@@ -7674,7 +7938,7 @@
       <c r="G131" s="18"/>
     </row>
     <row r="133" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B133" s="11" t="s">
+      <c r="B133" s="12" t="s">
         <v>462</v>
       </c>
       <c r="C133" s="18"/>
@@ -7687,7 +7951,7 @@
       <c r="B134" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="C134" s="11" t="s">
+      <c r="C134" s="12" t="s">
         <v>463</v>
       </c>
       <c r="D134" s="18"/>
@@ -7696,7 +7960,7 @@
       <c r="G134" s="18"/>
     </row>
     <row r="135" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B135" s="11" t="s">
+      <c r="B135" s="12" t="s">
         <v>370</v>
       </c>
       <c r="C135" s="18"/>
@@ -7825,7 +8089,7 @@
       </c>
     </row>
     <row r="143" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B143" s="11" t="s">
+      <c r="B143" s="12" t="s">
         <v>379</v>
       </c>
       <c r="C143" s="18"/>
@@ -7838,7 +8102,7 @@
       <c r="B144" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="C144" s="11" t="s">
+      <c r="C144" s="12" t="s">
         <v>426</v>
       </c>
       <c r="D144" s="18"/>
@@ -7869,7 +8133,7 @@
       </c>
     </row>
     <row r="147" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B147" s="11" t="s">
+      <c r="B147" s="12" t="s">
         <v>403</v>
       </c>
       <c r="C147" s="18"/>
@@ -7915,7 +8179,7 @@
       <c r="B151" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="C151" s="11" t="s">
+      <c r="C151" s="12" t="s">
         <v>474</v>
       </c>
       <c r="D151" s="18"/>
@@ -7924,7 +8188,7 @@
       <c r="G151" s="18"/>
     </row>
     <row r="153" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B153" s="11" t="s">
+      <c r="B153" s="12" t="s">
         <v>475</v>
       </c>
       <c r="C153" s="18"/>
@@ -7937,7 +8201,7 @@
       <c r="B154" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="C154" s="11" t="s">
+      <c r="C154" s="12" t="s">
         <v>463</v>
       </c>
       <c r="D154" s="18"/>
@@ -7946,7 +8210,7 @@
       <c r="G154" s="18"/>
     </row>
     <row r="155" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B155" s="11" t="s">
+      <c r="B155" s="12" t="s">
         <v>370</v>
       </c>
       <c r="C155" s="18"/>
@@ -8092,7 +8356,7 @@
       </c>
     </row>
     <row r="164" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B164" s="11" t="s">
+      <c r="B164" s="12" t="s">
         <v>379</v>
       </c>
       <c r="C164" s="18"/>
@@ -8105,7 +8369,7 @@
       <c r="B165" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="C165" s="11" t="s">
+      <c r="C165" s="12" t="s">
         <v>381</v>
       </c>
       <c r="D165" s="18"/>
@@ -8136,7 +8400,7 @@
       </c>
     </row>
     <row r="168" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B168" s="11" t="s">
+      <c r="B168" s="12" t="s">
         <v>403</v>
       </c>
       <c r="C168" s="18"/>
@@ -8193,7 +8457,7 @@
       <c r="B173" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="C173" s="11" t="s">
+      <c r="C173" s="12" t="s">
         <v>477</v>
       </c>
       <c r="D173" s="18"/>
@@ -8202,7 +8466,7 @@
       <c r="G173" s="18"/>
     </row>
     <row r="175" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B175" s="11" t="s">
+      <c r="B175" s="12" t="s">
         <v>478</v>
       </c>
       <c r="C175" s="18"/>
@@ -8215,7 +8479,7 @@
       <c r="B176" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="C176" s="11" t="s">
+      <c r="C176" s="12" t="s">
         <v>463</v>
       </c>
       <c r="D176" s="18"/>
@@ -8224,7 +8488,7 @@
       <c r="G176" s="18"/>
     </row>
     <row r="177" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B177" s="11" t="s">
+      <c r="B177" s="12" t="s">
         <v>370</v>
       </c>
       <c r="C177" s="18"/>
@@ -8268,7 +8532,7 @@
       </c>
     </row>
     <row r="180" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B180" s="11" t="s">
+      <c r="B180" s="12" t="s">
         <v>379</v>
       </c>
       <c r="C180" s="18"/>
@@ -8281,7 +8545,7 @@
       <c r="B181" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="C181" s="11" t="s">
+      <c r="C181" s="12" t="s">
         <v>479</v>
       </c>
       <c r="D181" s="18"/>
@@ -8290,7 +8554,7 @@
       <c r="G181" s="18"/>
     </row>
     <row r="182" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B182" s="11" t="s">
+      <c r="B182" s="12" t="s">
         <v>453</v>
       </c>
       <c r="C182" s="18"/>
@@ -8300,7 +8564,7 @@
       <c r="G182" s="18"/>
     </row>
     <row r="183" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B183" s="11" t="s">
+      <c r="B183" s="12" t="s">
         <v>403</v>
       </c>
       <c r="C183" s="18"/>
@@ -8357,7 +8621,7 @@
       <c r="B188" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="C188" s="11" t="s">
+      <c r="C188" s="12" t="s">
         <v>482</v>
       </c>
       <c r="D188" s="18"/>
@@ -8369,7 +8633,7 @@
       <c r="B189" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C189" s="11" t="s">
+      <c r="C189" s="12" t="s">
         <v>545</v>
       </c>
       <c r="D189" s="18"/>
@@ -8378,7 +8642,7 @@
       <c r="G189" s="18"/>
     </row>
     <row r="191" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B191" s="11" t="s">
+      <c r="B191" s="12" t="s">
         <v>483</v>
       </c>
       <c r="C191" s="18"/>
@@ -8391,7 +8655,7 @@
       <c r="B192" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="C192" s="11" t="s">
+      <c r="C192" s="12" t="s">
         <v>463</v>
       </c>
       <c r="D192" s="18"/>
@@ -8400,7 +8664,7 @@
       <c r="G192" s="18"/>
     </row>
     <row r="193" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B193" s="11" t="s">
+      <c r="B193" s="12" t="s">
         <v>370</v>
       </c>
       <c r="C193" s="18"/>
@@ -8461,7 +8725,7 @@
       </c>
     </row>
     <row r="197" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B197" s="11" t="s">
+      <c r="B197" s="12" t="s">
         <v>379</v>
       </c>
       <c r="C197" s="18"/>
@@ -8474,7 +8738,7 @@
       <c r="B198" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="C198" s="11" t="s">
+      <c r="C198" s="12" t="s">
         <v>381</v>
       </c>
       <c r="D198" s="18"/>
@@ -8576,7 +8840,7 @@
       </c>
     </row>
     <row r="208" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B208" s="11" t="s">
+      <c r="B208" s="12" t="s">
         <v>403</v>
       </c>
       <c r="C208" s="18"/>
@@ -8611,7 +8875,7 @@
       <c r="B211" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="C211" s="11" t="s">
+      <c r="C211" s="12" t="s">
         <v>494</v>
       </c>
       <c r="D211" s="18"/>
@@ -8623,7 +8887,7 @@
       <c r="B212" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C212" s="11" t="s">
+      <c r="C212" s="12" t="s">
         <v>546</v>
       </c>
       <c r="D212" s="18"/>
@@ -8632,7 +8896,7 @@
       <c r="G212" s="18"/>
     </row>
     <row r="214" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B214" s="11" t="s">
+      <c r="B214" s="12" t="s">
         <v>495</v>
       </c>
       <c r="C214" s="18"/>
@@ -8645,7 +8909,7 @@
       <c r="B215" s="7" t="s">
         <v>327</v>
       </c>
-      <c r="C215" s="11" t="s">
+      <c r="C215" s="12" t="s">
         <v>365</v>
       </c>
       <c r="D215" s="18"/>
@@ -8654,7 +8918,7 @@
       <c r="G215" s="18"/>
     </row>
     <row r="216" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B216" s="11" t="s">
+      <c r="B216" s="12" t="s">
         <v>370</v>
       </c>
       <c r="C216" s="18"/>
@@ -8698,7 +8962,7 @@
       </c>
     </row>
     <row r="219" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B219" s="11" t="s">
+      <c r="B219" s="12" t="s">
         <v>379</v>
       </c>
       <c r="C219" s="18"/>
@@ -8711,7 +8975,7 @@
       <c r="B220" s="7" t="s">
         <v>380</v>
       </c>
-      <c r="C220" s="11" t="s">
+      <c r="C220" s="12" t="s">
         <v>381</v>
       </c>
       <c r="D220" s="18"/>
@@ -8764,7 +9028,7 @@
       </c>
     </row>
     <row r="225" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B225" s="11" t="s">
+      <c r="B225" s="12" t="s">
         <v>403</v>
       </c>
       <c r="C225" s="18"/>
@@ -8799,7 +9063,7 @@
       <c r="B228" s="7" t="s">
         <v>404</v>
       </c>
-      <c r="C228" s="11" t="s">
+      <c r="C228" s="12" t="s">
         <v>503</v>
       </c>
       <c r="D228" s="18"/>
@@ -8811,7 +9075,7 @@
       <c r="B229" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C229" s="11" t="s">
+      <c r="C229" s="12" t="s">
         <v>504</v>
       </c>
       <c r="D229" s="18"/>
@@ -8820,7 +9084,7 @@
       <c r="G229" s="18"/>
     </row>
     <row r="231" spans="2:7" x14ac:dyDescent="0.55000000000000004">
-      <c r="B231" s="11" t="s">
+      <c r="B231" s="12" t="s">
         <v>505</v>
       </c>
       <c r="C231" s="18"/>
@@ -8895,6 +9159,96 @@
     </row>
   </sheetData>
   <mergeCells count="105">
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B4:G4"/>
+    <mergeCell ref="C5:G5"/>
+    <mergeCell ref="C6:G6"/>
+    <mergeCell ref="C7:G7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="C9:G9"/>
+    <mergeCell ref="C10:G10"/>
+    <mergeCell ref="C11:G11"/>
+    <mergeCell ref="C12:G12"/>
+    <mergeCell ref="C13:G13"/>
+    <mergeCell ref="C14:G14"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="C16:G16"/>
+    <mergeCell ref="C17:G17"/>
+    <mergeCell ref="C18:G18"/>
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C20:G20"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="B35:G35"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B40:G40"/>
+    <mergeCell ref="C41:G41"/>
+    <mergeCell ref="B42:G42"/>
+    <mergeCell ref="B45:G45"/>
+    <mergeCell ref="C46:G46"/>
+    <mergeCell ref="B57:G57"/>
+    <mergeCell ref="B58:G58"/>
+    <mergeCell ref="C59:G59"/>
+    <mergeCell ref="B61:G61"/>
+    <mergeCell ref="C62:G62"/>
+    <mergeCell ref="B63:G63"/>
+    <mergeCell ref="B66:G66"/>
+    <mergeCell ref="C67:G67"/>
+    <mergeCell ref="B72:G72"/>
+    <mergeCell ref="C75:G75"/>
+    <mergeCell ref="C76:G76"/>
+    <mergeCell ref="B78:G78"/>
+    <mergeCell ref="C79:G79"/>
+    <mergeCell ref="B80:G80"/>
+    <mergeCell ref="B83:G83"/>
+    <mergeCell ref="C84:G84"/>
+    <mergeCell ref="B91:G91"/>
+    <mergeCell ref="C97:G97"/>
+    <mergeCell ref="C98:G98"/>
+    <mergeCell ref="B100:G100"/>
+    <mergeCell ref="C101:G101"/>
+    <mergeCell ref="B102:G102"/>
+    <mergeCell ref="B103:G103"/>
+    <mergeCell ref="B104:G104"/>
+    <mergeCell ref="C105:G105"/>
+    <mergeCell ref="B114:G114"/>
+    <mergeCell ref="B115:G115"/>
+    <mergeCell ref="C116:G116"/>
+    <mergeCell ref="B118:G118"/>
+    <mergeCell ref="C119:G119"/>
+    <mergeCell ref="B120:G120"/>
+    <mergeCell ref="B123:G123"/>
+    <mergeCell ref="C124:G124"/>
+    <mergeCell ref="B125:G125"/>
+    <mergeCell ref="B126:G126"/>
+    <mergeCell ref="C131:G131"/>
+    <mergeCell ref="B133:G133"/>
+    <mergeCell ref="C134:G134"/>
+    <mergeCell ref="B135:G135"/>
+    <mergeCell ref="B143:G143"/>
+    <mergeCell ref="C144:G144"/>
+    <mergeCell ref="B147:G147"/>
+    <mergeCell ref="C151:G151"/>
+    <mergeCell ref="B153:G153"/>
+    <mergeCell ref="C154:G154"/>
+    <mergeCell ref="B155:G155"/>
+    <mergeCell ref="B164:G164"/>
+    <mergeCell ref="C165:G165"/>
+    <mergeCell ref="B168:G168"/>
+    <mergeCell ref="C173:G173"/>
+    <mergeCell ref="B175:G175"/>
+    <mergeCell ref="C176:G176"/>
+    <mergeCell ref="B177:G177"/>
+    <mergeCell ref="B180:G180"/>
+    <mergeCell ref="C181:G181"/>
+    <mergeCell ref="B182:G182"/>
+    <mergeCell ref="B183:G183"/>
+    <mergeCell ref="C188:G188"/>
+    <mergeCell ref="C189:G189"/>
+    <mergeCell ref="B191:G191"/>
+    <mergeCell ref="C192:G192"/>
     <mergeCell ref="B219:G219"/>
     <mergeCell ref="C220:G220"/>
     <mergeCell ref="B225:G225"/>
@@ -8910,96 +9264,6 @@
     <mergeCell ref="B214:G214"/>
     <mergeCell ref="C215:G215"/>
     <mergeCell ref="B216:G216"/>
-    <mergeCell ref="B177:G177"/>
-    <mergeCell ref="B180:G180"/>
-    <mergeCell ref="C181:G181"/>
-    <mergeCell ref="B182:G182"/>
-    <mergeCell ref="B183:G183"/>
-    <mergeCell ref="C188:G188"/>
-    <mergeCell ref="C189:G189"/>
-    <mergeCell ref="B191:G191"/>
-    <mergeCell ref="C192:G192"/>
-    <mergeCell ref="B153:G153"/>
-    <mergeCell ref="C154:G154"/>
-    <mergeCell ref="B155:G155"/>
-    <mergeCell ref="B164:G164"/>
-    <mergeCell ref="C165:G165"/>
-    <mergeCell ref="B168:G168"/>
-    <mergeCell ref="C173:G173"/>
-    <mergeCell ref="B175:G175"/>
-    <mergeCell ref="C176:G176"/>
-    <mergeCell ref="B126:G126"/>
-    <mergeCell ref="C131:G131"/>
-    <mergeCell ref="B133:G133"/>
-    <mergeCell ref="C134:G134"/>
-    <mergeCell ref="B135:G135"/>
-    <mergeCell ref="B143:G143"/>
-    <mergeCell ref="C144:G144"/>
-    <mergeCell ref="B147:G147"/>
-    <mergeCell ref="C151:G151"/>
-    <mergeCell ref="B114:G114"/>
-    <mergeCell ref="B115:G115"/>
-    <mergeCell ref="C116:G116"/>
-    <mergeCell ref="B118:G118"/>
-    <mergeCell ref="C119:G119"/>
-    <mergeCell ref="B120:G120"/>
-    <mergeCell ref="B123:G123"/>
-    <mergeCell ref="C124:G124"/>
-    <mergeCell ref="B125:G125"/>
-    <mergeCell ref="B91:G91"/>
-    <mergeCell ref="C97:G97"/>
-    <mergeCell ref="C98:G98"/>
-    <mergeCell ref="B100:G100"/>
-    <mergeCell ref="C101:G101"/>
-    <mergeCell ref="B102:G102"/>
-    <mergeCell ref="B103:G103"/>
-    <mergeCell ref="B104:G104"/>
-    <mergeCell ref="C105:G105"/>
-    <mergeCell ref="C67:G67"/>
-    <mergeCell ref="B72:G72"/>
-    <mergeCell ref="C75:G75"/>
-    <mergeCell ref="C76:G76"/>
-    <mergeCell ref="B78:G78"/>
-    <mergeCell ref="C79:G79"/>
-    <mergeCell ref="B80:G80"/>
-    <mergeCell ref="B83:G83"/>
-    <mergeCell ref="C84:G84"/>
-    <mergeCell ref="B45:G45"/>
-    <mergeCell ref="C46:G46"/>
-    <mergeCell ref="B57:G57"/>
-    <mergeCell ref="B58:G58"/>
-    <mergeCell ref="C59:G59"/>
-    <mergeCell ref="B61:G61"/>
-    <mergeCell ref="C62:G62"/>
-    <mergeCell ref="B63:G63"/>
-    <mergeCell ref="B66:G66"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="B22:G22"/>
-    <mergeCell ref="B34:G34"/>
-    <mergeCell ref="B35:G35"/>
-    <mergeCell ref="B36:G36"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="B40:G40"/>
-    <mergeCell ref="C41:G41"/>
-    <mergeCell ref="B42:G42"/>
-    <mergeCell ref="C11:G11"/>
-    <mergeCell ref="C12:G12"/>
-    <mergeCell ref="C13:G13"/>
-    <mergeCell ref="C14:G14"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="C16:G16"/>
-    <mergeCell ref="C17:G17"/>
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="B1:G1"/>
-    <mergeCell ref="B2:G2"/>
-    <mergeCell ref="B4:G4"/>
-    <mergeCell ref="C5:G5"/>
-    <mergeCell ref="C6:G6"/>
-    <mergeCell ref="C7:G7"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="C9:G9"/>
-    <mergeCell ref="C10:G10"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9017,17 +9281,17 @@
     <col min="6" max="6" width="25.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B2" t="s">
         <v>550</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B3" t="s">
         <v>555</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B4" s="4" t="s">
         <v>556</v>
       </c>
@@ -9043,10 +9307,8 @@
       <c r="F4" s="4" t="s">
         <v>559</v>
       </c>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B5" s="4" t="s">
         <v>560</v>
       </c>
@@ -9062,10 +9324,8 @@
       <c r="F5" s="4" t="s">
         <v>564</v>
       </c>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B6" s="4"/>
       <c r="C6" s="4" t="s">
         <v>573</v>
@@ -9079,10 +9339,8 @@
       <c r="F6" s="4" t="s">
         <v>565</v>
       </c>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B7" s="4"/>
       <c r="C7" s="4" t="s">
         <v>574</v>
@@ -9096,10 +9354,8 @@
       <c r="F7" s="4" t="s">
         <v>564</v>
       </c>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B8" s="4"/>
       <c r="C8" s="4" t="s">
         <v>575</v>
@@ -9113,10 +9369,8 @@
       <c r="F8" s="4" t="s">
         <v>566</v>
       </c>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B9" s="4"/>
       <c r="C9" s="4" t="s">
         <v>576</v>
@@ -9130,10 +9384,8 @@
       <c r="F9" s="4" t="s">
         <v>568</v>
       </c>
-      <c r="G9" s="19"/>
-      <c r="H9" s="19"/>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B10" s="4"/>
       <c r="C10" s="4" t="s">
         <v>554</v>
@@ -9147,10 +9399,8 @@
       <c r="F10" s="4" t="s">
         <v>567</v>
       </c>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B11" s="4" t="s">
         <v>580</v>
       </c>
@@ -9166,10 +9416,8 @@
       <c r="F11" s="4" t="s">
         <v>582</v>
       </c>
-      <c r="G11" s="19"/>
-      <c r="H11" s="19"/>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B12" s="4" t="s">
         <v>579</v>
       </c>
@@ -9185,15 +9433,13 @@
       <c r="F12" s="4" t="s">
         <v>583</v>
       </c>
-      <c r="G12" s="19"/>
-      <c r="H12" s="19"/>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B14" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B15" s="4" t="s">
         <v>585</v>
       </c>
@@ -9204,7 +9450,7 @@
       <c r="E15" s="4"/>
       <c r="F15" s="4"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.55000000000000004">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.55000000000000004">
       <c r="B16" s="4" t="s">
         <v>586</v>
       </c>
@@ -9584,10 +9830,8 @@
       <c r="B52" t="s">
         <v>638</v>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t xml:space="preserve">VARCHAR(1000)</t>
-        </is>
+      <c r="C52" t="s">
+        <v>651</v>
       </c>
       <c r="D52" t="s">
         <v>642</v>
@@ -9649,10 +9893,8 @@
       <c r="C59" t="s">
         <v>622</v>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t xml:space="preserve">NOT NULL, FK→events.id, ON DELETE CASCADE（要確認・推奨値）</t>
-        </is>
+      <c r="D59" t="s">
+        <v>652</v>
       </c>
     </row>
     <row r="60" spans="2:4" x14ac:dyDescent="0.55000000000000004">
@@ -9663,7 +9905,7 @@
         <v>625</v>
       </c>
       <c r="D60" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="61" spans="2:4" x14ac:dyDescent="0.55000000000000004">
@@ -9688,106 +9930,70 @@
         <v>643</v>
       </c>
     </row>
-    <row r="64" spans="2:6">
-      <c r="B64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">インデックス一覧</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" spans="2:6">
-      <c r="B65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">テーブル</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">インデックス名</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">対象列</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">用途</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" spans="2:6">
-      <c r="B66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">events</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">idx_events_start_at</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">start_at</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">一覧の開催日時昇順ソート（API-01）</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" spans="2:6">
-      <c r="B67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">applications</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">idx_app_event_status_user</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">event_id, status, user_id</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">定員超過チェック・充足率集計（event_id+status）、二重申込チェック（+user_id）</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" spans="2:6">
-      <c r="B68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">applications</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">idx_app_user_applied</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">user_id, applied_at</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">マイページの自分の申込一覧（API-04、申込日時順）</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" spans="2:6">
-      <c r="B69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">※ user_id／event_id 単体には、FK制約によりMySQL(InnoDB)が自動でインデックスを作成する。</t>
-        </is>
+    <row r="64" spans="2:4" x14ac:dyDescent="0.55000000000000004">
+      <c r="B64" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="65" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B65" t="s">
+        <v>654</v>
+      </c>
+      <c r="C65" t="s">
+        <v>655</v>
+      </c>
+      <c r="D65" t="s">
+        <v>656</v>
+      </c>
+      <c r="E65" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="66" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B66" t="s">
+        <v>658</v>
+      </c>
+      <c r="C66" t="s">
+        <v>659</v>
+      </c>
+      <c r="D66" t="s">
+        <v>660</v>
+      </c>
+      <c r="E66" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="67" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B67" t="s">
+        <v>662</v>
+      </c>
+      <c r="C67" t="s">
+        <v>663</v>
+      </c>
+      <c r="D67" t="s">
+        <v>664</v>
+      </c>
+      <c r="E67" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="68" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B68" t="s">
+        <v>662</v>
+      </c>
+      <c r="C68" t="s">
+        <v>666</v>
+      </c>
+      <c r="D68" t="s">
+        <v>667</v>
+      </c>
+      <c r="E68" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="69" spans="2:5" x14ac:dyDescent="0.55000000000000004">
+      <c r="B69" t="s">
+        <v>669</v>
       </c>
     </row>
   </sheetData>
